--- a/output/yearly_population_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_20_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6592</v>
+        <v>6125</v>
       </c>
       <c r="C2" t="n">
-        <v>8085</v>
+        <v>6224</v>
       </c>
       <c r="D2" t="n">
-        <v>22198</v>
+        <v>31922</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4231</v>
+        <v>3674</v>
       </c>
       <c r="C3" t="n">
-        <v>5011</v>
+        <v>5677</v>
       </c>
       <c r="D3" t="n">
-        <v>14381</v>
+        <v>14396</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3384</v>
+        <v>3010</v>
       </c>
       <c r="C4" t="n">
-        <v>5812</v>
+        <v>4649</v>
       </c>
       <c r="D4" t="n">
-        <v>7280</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2105</v>
+        <v>1967</v>
       </c>
       <c r="C5" t="n">
-        <v>4264</v>
+        <v>3520</v>
       </c>
       <c r="D5" t="n">
-        <v>2844</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1104</v>
+        <v>1050</v>
       </c>
       <c r="C6" t="n">
-        <v>2365</v>
+        <v>2144</v>
       </c>
       <c r="D6" t="n">
-        <v>1185</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="C7" t="n">
-        <v>1353</v>
+        <v>1261</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C8" t="n">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7802</v>
+        <v>7892</v>
       </c>
       <c r="C2" t="n">
-        <v>14917</v>
+        <v>6043</v>
       </c>
       <c r="D2" t="n">
-        <v>17491</v>
+        <v>24344</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4305</v>
+        <v>3940</v>
       </c>
       <c r="C3" t="n">
-        <v>5655</v>
+        <v>5205</v>
       </c>
       <c r="D3" t="n">
-        <v>14477</v>
+        <v>15929</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3215</v>
+        <v>2833</v>
       </c>
       <c r="C4" t="n">
-        <v>5298</v>
+        <v>5020</v>
       </c>
       <c r="D4" t="n">
-        <v>8147</v>
+        <v>7624</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2349</v>
+        <v>2149</v>
       </c>
       <c r="C5" t="n">
-        <v>4862</v>
+        <v>3999</v>
       </c>
       <c r="D5" t="n">
-        <v>3481</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1410</v>
+        <v>1337</v>
       </c>
       <c r="C6" t="n">
-        <v>3216</v>
+        <v>2769</v>
       </c>
       <c r="D6" t="n">
-        <v>1412</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>688</v>
+        <v>666</v>
       </c>
       <c r="C7" t="n">
-        <v>1795</v>
+        <v>1654</v>
       </c>
       <c r="D7" t="n">
-        <v>733</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C8" t="n">
-        <v>956</v>
+        <v>934</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10155</v>
+        <v>10306</v>
       </c>
       <c r="C2" t="n">
-        <v>11858</v>
+        <v>5600</v>
       </c>
       <c r="D2" t="n">
-        <v>19838</v>
+        <v>24653</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4671</v>
+        <v>4539</v>
       </c>
       <c r="C3" t="n">
-        <v>8540</v>
+        <v>4918</v>
       </c>
       <c r="D3" t="n">
-        <v>13913</v>
+        <v>15961</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3156</v>
+        <v>2815</v>
       </c>
       <c r="C4" t="n">
-        <v>5294</v>
+        <v>4952</v>
       </c>
       <c r="D4" t="n">
-        <v>8871</v>
+        <v>8594</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2402</v>
+        <v>2192</v>
       </c>
       <c r="C5" t="n">
-        <v>4902</v>
+        <v>4376</v>
       </c>
       <c r="D5" t="n">
-        <v>4013</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1628</v>
+        <v>1525</v>
       </c>
       <c r="C6" t="n">
-        <v>3881</v>
+        <v>3247</v>
       </c>
       <c r="D6" t="n">
-        <v>1691</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>875</v>
+        <v>844</v>
       </c>
       <c r="C7" t="n">
-        <v>2361</v>
+        <v>2134</v>
       </c>
       <c r="D7" t="n">
-        <v>811</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C8" t="n">
-        <v>1283</v>
+        <v>1220</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C9" t="n">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9129</v>
+        <v>9145</v>
       </c>
       <c r="C2" t="n">
-        <v>7968</v>
+        <v>3718</v>
       </c>
       <c r="D2" t="n">
-        <v>16404</v>
+        <v>20138</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5673</v>
+        <v>5376</v>
       </c>
       <c r="C3" t="n">
-        <v>11850</v>
+        <v>7384</v>
       </c>
       <c r="D3" t="n">
-        <v>15462</v>
+        <v>17464</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2219</v>
+        <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>7653</v>
+        <v>7053</v>
       </c>
       <c r="D4" t="n">
-        <v>8611</v>
+        <v>8155</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1504</v>
+        <v>1409</v>
       </c>
       <c r="C5" t="n">
-        <v>3803</v>
+        <v>3182</v>
       </c>
       <c r="D5" t="n">
-        <v>2774</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>808</v>
+        <v>779</v>
       </c>
       <c r="C6" t="n">
-        <v>2313</v>
+        <v>2091</v>
       </c>
       <c r="D6" t="n">
-        <v>794</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C7" t="n">
-        <v>1257</v>
+        <v>1195</v>
       </c>
       <c r="D7" t="n">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
         <v>204</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>39</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5559</v>
+        <v>5302</v>
       </c>
       <c r="C2" t="n">
-        <v>3518</v>
+        <v>1823</v>
       </c>
       <c r="D2" t="n">
-        <v>12467</v>
+        <v>13784</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6136</v>
+        <v>6004</v>
       </c>
       <c r="C3" t="n">
-        <v>9116</v>
+        <v>5079</v>
       </c>
       <c r="D3" t="n">
-        <v>14699</v>
+        <v>16982</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3090</v>
+        <v>2908</v>
       </c>
       <c r="C4" t="n">
-        <v>9688</v>
+        <v>7339</v>
       </c>
       <c r="D4" t="n">
-        <v>9566</v>
+        <v>9415</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1686</v>
+        <v>1572</v>
       </c>
       <c r="C5" t="n">
-        <v>5532</v>
+        <v>4940</v>
       </c>
       <c r="D5" t="n">
-        <v>3471</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>978</v>
+        <v>948</v>
       </c>
       <c r="C6" t="n">
-        <v>2982</v>
+        <v>2615</v>
       </c>
       <c r="D6" t="n">
-        <v>997</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>1644</v>
+        <v>1542</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>38</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5970</v>
+        <v>7050</v>
       </c>
       <c r="C2" t="n">
-        <v>9236</v>
+        <v>9033</v>
       </c>
       <c r="D2" t="n">
-        <v>15033</v>
+        <v>24709</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4944</v>
+        <v>4824</v>
       </c>
       <c r="C3" t="n">
-        <v>5692</v>
+        <v>3030</v>
       </c>
       <c r="D3" t="n">
-        <v>13507</v>
+        <v>15353</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3801</v>
+        <v>3661</v>
       </c>
       <c r="C4" t="n">
-        <v>9200</v>
+        <v>6085</v>
       </c>
       <c r="D4" t="n">
-        <v>10021</v>
+        <v>10436</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>1916</v>
       </c>
       <c r="C5" t="n">
-        <v>7464</v>
+        <v>6011</v>
       </c>
       <c r="D5" t="n">
-        <v>4360</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1166</v>
+        <v>1130</v>
       </c>
       <c r="C6" t="n">
-        <v>4103</v>
+        <v>3707</v>
       </c>
       <c r="D6" t="n">
-        <v>1363</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C7" t="n">
-        <v>2249</v>
+        <v>2040</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>1179</v>
+        <v>1142</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3544</v>
+        <v>4053</v>
       </c>
       <c r="C2" t="n">
-        <v>4251</v>
+        <v>4078</v>
       </c>
       <c r="D2" t="n">
-        <v>10388</v>
+        <v>17059</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5007</v>
+        <v>5200</v>
       </c>
       <c r="C3" t="n">
-        <v>6728</v>
+        <v>5012</v>
       </c>
       <c r="D3" t="n">
-        <v>13483</v>
+        <v>16032</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4202</v>
+        <v>4095</v>
       </c>
       <c r="C4" t="n">
-        <v>8801</v>
+        <v>5515</v>
       </c>
       <c r="D4" t="n">
-        <v>10540</v>
+        <v>11091</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2098</v>
+        <v>2015</v>
       </c>
       <c r="C5" t="n">
-        <v>8879</v>
+        <v>6819</v>
       </c>
       <c r="D5" t="n">
-        <v>4579</v>
+        <v>4506</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C6" t="n">
-        <v>4955</v>
+        <v>4585</v>
       </c>
       <c r="D6" t="n">
-        <v>1334</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>2284</v>
+        <v>2149</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>910</v>
+        <v>924</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>36</v>
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4723</v>
+        <v>4549</v>
       </c>
       <c r="C2" t="n">
-        <v>5030</v>
+        <v>3053</v>
       </c>
       <c r="D2" t="n">
-        <v>8119</v>
+        <v>19553</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3764</v>
+        <v>4008</v>
       </c>
       <c r="C3" t="n">
-        <v>4994</v>
+        <v>4054</v>
       </c>
       <c r="D3" t="n">
-        <v>12156</v>
+        <v>15230</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3954</v>
+        <v>4014</v>
       </c>
       <c r="C4" t="n">
-        <v>7642</v>
+        <v>5154</v>
       </c>
       <c r="D4" t="n">
-        <v>10801</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2607</v>
+        <v>2538</v>
       </c>
       <c r="C5" t="n">
-        <v>8744</v>
+        <v>6129</v>
       </c>
       <c r="D5" t="n">
-        <v>5298</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1265</v>
+        <v>1240</v>
       </c>
       <c r="C6" t="n">
-        <v>6615</v>
+        <v>5617</v>
       </c>
       <c r="D6" t="n">
-        <v>1752</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="C7" t="n">
-        <v>3401</v>
+        <v>3171</v>
       </c>
       <c r="D7" t="n">
-        <v>686</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1425</v>
+        <v>1409</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3325</v>
+        <v>3184</v>
       </c>
       <c r="C2" t="n">
-        <v>2872</v>
+        <v>1802</v>
       </c>
       <c r="D2" t="n">
-        <v>6442</v>
+        <v>13701</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3567</v>
+        <v>3668</v>
       </c>
       <c r="C3" t="n">
-        <v>4591</v>
+        <v>3327</v>
       </c>
       <c r="D3" t="n">
-        <v>11010</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3556</v>
+        <v>3691</v>
       </c>
       <c r="C4" t="n">
-        <v>6562</v>
+        <v>4681</v>
       </c>
       <c r="D4" t="n">
-        <v>10758</v>
+        <v>11812</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2870</v>
+        <v>2837</v>
       </c>
       <c r="C5" t="n">
-        <v>8495</v>
+        <v>5862</v>
       </c>
       <c r="D5" t="n">
-        <v>5872</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1508</v>
+        <v>1471</v>
       </c>
       <c r="C6" t="n">
-        <v>7548</v>
+        <v>6018</v>
       </c>
       <c r="D6" t="n">
-        <v>2071</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>4420</v>
+        <v>4034</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1883</v>
+        <v>1872</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>611</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4685</v>
+        <v>4226</v>
       </c>
       <c r="C2" t="n">
-        <v>7975</v>
+        <v>8763</v>
       </c>
       <c r="D2" t="n">
-        <v>6977</v>
+        <v>12746</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C3" t="n">
-        <v>3479</v>
+        <v>2402</v>
       </c>
       <c r="D3" t="n">
-        <v>9757</v>
+        <v>13911</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3123</v>
+        <v>3231</v>
       </c>
       <c r="C4" t="n">
-        <v>5592</v>
+        <v>3985</v>
       </c>
       <c r="D4" t="n">
-        <v>10467</v>
+        <v>11954</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2829</v>
+        <v>2856</v>
       </c>
       <c r="C5" t="n">
-        <v>7538</v>
+        <v>5241</v>
       </c>
       <c r="D5" t="n">
-        <v>6350</v>
+        <v>6638</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1825</v>
+        <v>1816</v>
       </c>
       <c r="C6" t="n">
-        <v>7848</v>
+        <v>5902</v>
       </c>
       <c r="D6" t="n">
-        <v>2518</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>611</v>
+        <v>653</v>
       </c>
       <c r="C7" t="n">
-        <v>5583</v>
+        <v>4810</v>
       </c>
       <c r="D7" t="n">
-        <v>923</v>
+        <v>910</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>2795</v>
+        <v>2694</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>998</v>
+        <v>1049</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>140</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
         <v>65</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" t="n">
         <v>39</v>
-      </c>
-      <c r="D14" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6118</v>
+        <v>5194</v>
       </c>
       <c r="C2" t="n">
-        <v>5110</v>
+        <v>4281</v>
       </c>
       <c r="D2" t="n">
-        <v>9771</v>
+        <v>5679</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3353</v>
+        <v>2962</v>
       </c>
       <c r="C2" t="n">
-        <v>4594</v>
+        <v>4837</v>
       </c>
       <c r="D2" t="n">
-        <v>5135</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3918</v>
+        <v>3926</v>
       </c>
       <c r="C3" t="n">
-        <v>4792</v>
+        <v>4179</v>
       </c>
       <c r="D3" t="n">
-        <v>10516</v>
+        <v>14858</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4185</v>
+        <v>4295</v>
       </c>
       <c r="C4" t="n">
-        <v>8090</v>
+        <v>5634</v>
       </c>
       <c r="D4" t="n">
-        <v>10868</v>
+        <v>12316</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1764</v>
+        <v>1783</v>
       </c>
       <c r="C5" t="n">
-        <v>11001</v>
+        <v>8033</v>
       </c>
       <c r="D5" t="n">
-        <v>5805</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>564</v>
+        <v>603</v>
       </c>
       <c r="C6" t="n">
-        <v>7009</v>
+        <v>5986</v>
       </c>
       <c r="D6" t="n">
-        <v>2020</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>2739</v>
+        <v>2640</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>978</v>
+        <v>1028</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D10" t="n">
         <v>137</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6353</v>
+        <v>6732</v>
       </c>
       <c r="C2" t="n">
-        <v>2955</v>
+        <v>5007</v>
       </c>
       <c r="D2" t="n">
-        <v>15224</v>
+        <v>15575</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2599</v>
+        <v>2207</v>
       </c>
       <c r="C3" t="n">
-        <v>2575</v>
+        <v>2191</v>
       </c>
       <c r="D3" t="n">
-        <v>2280</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5383</v>
+        <v>4931</v>
       </c>
       <c r="C2" t="n">
-        <v>5891</v>
+        <v>3228</v>
       </c>
       <c r="D2" t="n">
-        <v>17400</v>
+        <v>14227</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3677</v>
+        <v>3668</v>
       </c>
       <c r="C3" t="n">
-        <v>2405</v>
+        <v>3282</v>
       </c>
       <c r="D3" t="n">
-        <v>4286</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1162</v>
+        <v>992</v>
       </c>
       <c r="C4" t="n">
-        <v>1576</v>
+        <v>1347</v>
       </c>
       <c r="D4" t="n">
-        <v>1640</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5568</v>
+        <v>4864</v>
       </c>
       <c r="C2" t="n">
-        <v>5994</v>
+        <v>3692</v>
       </c>
       <c r="D2" t="n">
-        <v>33731</v>
+        <v>19714</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3707</v>
+        <v>3534</v>
       </c>
       <c r="C3" t="n">
-        <v>3727</v>
+        <v>2841</v>
       </c>
       <c r="D3" t="n">
-        <v>6075</v>
+        <v>5239</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2049</v>
+        <v>2002</v>
       </c>
       <c r="C4" t="n">
-        <v>2012</v>
+        <v>2402</v>
       </c>
       <c r="D4" t="n">
-        <v>2098</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>537</v>
+        <v>468</v>
       </c>
       <c r="C5" t="n">
-        <v>955</v>
+        <v>842</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
         <v>303</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5277,7 +5277,7 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>211</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6486</v>
+        <v>5885</v>
       </c>
       <c r="C2" t="n">
-        <v>5017</v>
+        <v>7334</v>
       </c>
       <c r="D2" t="n">
-        <v>28452</v>
+        <v>22680</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3767</v>
+        <v>3463</v>
       </c>
       <c r="C3" t="n">
-        <v>4259</v>
+        <v>2856</v>
       </c>
       <c r="D3" t="n">
-        <v>9851</v>
+        <v>7070</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2427</v>
+        <v>2336</v>
       </c>
       <c r="C4" t="n">
-        <v>2872</v>
+        <v>2592</v>
       </c>
       <c r="D4" t="n">
-        <v>2739</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1080</v>
+        <v>1022</v>
       </c>
       <c r="C5" t="n">
-        <v>1493</v>
+        <v>1640</v>
       </c>
       <c r="D5" t="n">
-        <v>1343</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>631</v>
+        <v>579</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>123</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8244</v>
+        <v>7569</v>
       </c>
       <c r="C2" t="n">
-        <v>11814</v>
+        <v>6998</v>
       </c>
       <c r="D2" t="n">
-        <v>23016</v>
+        <v>28191</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3717</v>
+        <v>3390</v>
       </c>
       <c r="C3" t="n">
-        <v>3809</v>
+        <v>4247</v>
       </c>
       <c r="D3" t="n">
-        <v>11275</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1935</v>
+        <v>1799</v>
       </c>
       <c r="C4" t="n">
-        <v>2993</v>
+        <v>2227</v>
       </c>
       <c r="D4" t="n">
-        <v>3429</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>913</v>
+        <v>887</v>
       </c>
       <c r="C5" t="n">
-        <v>1625</v>
+        <v>1574</v>
       </c>
       <c r="D5" t="n">
-        <v>1262</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>714</v>
+        <v>757</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5986,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6518</v>
+        <v>5288</v>
       </c>
       <c r="C2" t="n">
-        <v>7240</v>
+        <v>6540</v>
       </c>
       <c r="D2" t="n">
-        <v>21631</v>
+        <v>26328</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5049</v>
+        <v>4598</v>
       </c>
       <c r="C3" t="n">
-        <v>7365</v>
+        <v>5065</v>
       </c>
       <c r="D3" t="n">
-        <v>12493</v>
+        <v>11262</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2469</v>
+        <v>2295</v>
       </c>
       <c r="C4" t="n">
-        <v>3432</v>
+        <v>3441</v>
       </c>
       <c r="D4" t="n">
-        <v>4981</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1279</v>
+        <v>1198</v>
       </c>
       <c r="C5" t="n">
-        <v>2405</v>
+        <v>1936</v>
       </c>
       <c r="D5" t="n">
-        <v>1660</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="C6" t="n">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="D6" t="n">
-        <v>843</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="D7" t="n">
         <v>563</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5551</v>
+        <v>4876</v>
       </c>
       <c r="C2" t="n">
-        <v>5202</v>
+        <v>7846</v>
       </c>
       <c r="D2" t="n">
-        <v>27827</v>
+        <v>28391</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4758</v>
+        <v>4077</v>
       </c>
       <c r="C3" t="n">
-        <v>6303</v>
+        <v>5087</v>
       </c>
       <c r="D3" t="n">
-        <v>13055</v>
+        <v>12964</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3244</v>
+        <v>2995</v>
       </c>
       <c r="C4" t="n">
-        <v>5626</v>
+        <v>4320</v>
       </c>
       <c r="D4" t="n">
-        <v>6224</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1636</v>
+        <v>1533</v>
       </c>
       <c r="C5" t="n">
-        <v>2926</v>
+        <v>2748</v>
       </c>
       <c r="D5" t="n">
-        <v>2247</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>811</v>
       </c>
       <c r="C6" t="n">
-        <v>1846</v>
+        <v>1587</v>
       </c>
       <c r="D6" t="n">
-        <v>980</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_20_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6125</v>
+        <v>4292</v>
       </c>
       <c r="C2" t="n">
-        <v>6224</v>
+        <v>7114</v>
       </c>
       <c r="D2" t="n">
-        <v>31922</v>
+        <v>26338</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3674</v>
+        <v>3162</v>
       </c>
       <c r="C3" t="n">
-        <v>5677</v>
+        <v>5013</v>
       </c>
       <c r="D3" t="n">
-        <v>14396</v>
+        <v>15049</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3010</v>
+        <v>2413</v>
       </c>
       <c r="C4" t="n">
-        <v>4649</v>
+        <v>4536</v>
       </c>
       <c r="D4" t="n">
-        <v>6447</v>
+        <v>8017</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1967</v>
+        <v>1648</v>
       </c>
       <c r="C5" t="n">
-        <v>3520</v>
+        <v>5301</v>
       </c>
       <c r="D5" t="n">
-        <v>2438</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1050</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>2144</v>
+        <v>4478</v>
       </c>
       <c r="D6" t="n">
-        <v>1078</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>503</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>1261</v>
+        <v>2776</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>667</v>
+        <v>1253</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>473</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7892</v>
+        <v>5227</v>
       </c>
       <c r="C2" t="n">
-        <v>6043</v>
+        <v>6409</v>
       </c>
       <c r="D2" t="n">
-        <v>24344</v>
+        <v>29555</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3940</v>
+        <v>2982</v>
       </c>
       <c r="C3" t="n">
-        <v>5205</v>
+        <v>5225</v>
       </c>
       <c r="D3" t="n">
-        <v>15929</v>
+        <v>15506</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2833</v>
+        <v>2325</v>
       </c>
       <c r="C4" t="n">
-        <v>5020</v>
+        <v>4613</v>
       </c>
       <c r="D4" t="n">
-        <v>7624</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2149</v>
+        <v>1740</v>
       </c>
       <c r="C5" t="n">
-        <v>3999</v>
+        <v>4852</v>
       </c>
       <c r="D5" t="n">
-        <v>2994</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>1087</v>
       </c>
       <c r="C6" t="n">
-        <v>2769</v>
+        <v>4740</v>
       </c>
       <c r="D6" t="n">
-        <v>1285</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>666</v>
+        <v>529</v>
       </c>
       <c r="C7" t="n">
-        <v>1654</v>
+        <v>3492</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>285</v>
+        <v>208</v>
       </c>
       <c r="C8" t="n">
-        <v>934</v>
+        <v>1852</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>468</v>
+        <v>773</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10306</v>
+        <v>7033</v>
       </c>
       <c r="C2" t="n">
-        <v>5600</v>
+        <v>11770</v>
       </c>
       <c r="D2" t="n">
-        <v>24653</v>
+        <v>24182</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4539</v>
+        <v>3131</v>
       </c>
       <c r="C3" t="n">
-        <v>4918</v>
+        <v>5063</v>
       </c>
       <c r="D3" t="n">
-        <v>15961</v>
+        <v>16199</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2815</v>
+        <v>2202</v>
       </c>
       <c r="C4" t="n">
-        <v>4952</v>
+        <v>4725</v>
       </c>
       <c r="D4" t="n">
-        <v>8594</v>
+        <v>9478</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2192</v>
+        <v>1770</v>
       </c>
       <c r="C5" t="n">
-        <v>4376</v>
+        <v>4654</v>
       </c>
       <c r="D5" t="n">
-        <v>3614</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1525</v>
+        <v>1213</v>
       </c>
       <c r="C6" t="n">
-        <v>3247</v>
+        <v>4696</v>
       </c>
       <c r="D6" t="n">
-        <v>1501</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>844</v>
+        <v>658</v>
       </c>
       <c r="C7" t="n">
-        <v>2134</v>
+        <v>3933</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>389</v>
+        <v>286</v>
       </c>
       <c r="C8" t="n">
-        <v>1220</v>
+        <v>2461</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>1145</v>
       </c>
       <c r="D9" t="n">
-        <v>340</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>469</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9145</v>
+        <v>6352</v>
       </c>
       <c r="C2" t="n">
-        <v>3718</v>
+        <v>8191</v>
       </c>
       <c r="D2" t="n">
-        <v>20138</v>
+        <v>20123</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5376</v>
+        <v>3823</v>
       </c>
       <c r="C3" t="n">
-        <v>7384</v>
+        <v>8125</v>
       </c>
       <c r="D3" t="n">
-        <v>17464</v>
+        <v>17685</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2025</v>
+        <v>1635</v>
       </c>
       <c r="C4" t="n">
-        <v>7053</v>
+        <v>6962</v>
       </c>
       <c r="D4" t="n">
-        <v>8155</v>
+        <v>9156</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1409</v>
+        <v>1120</v>
       </c>
       <c r="C5" t="n">
-        <v>3182</v>
+        <v>4602</v>
       </c>
       <c r="D5" t="n">
-        <v>2477</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>779</v>
+        <v>607</v>
       </c>
       <c r="C6" t="n">
-        <v>2091</v>
+        <v>3854</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>1195</v>
+        <v>2411</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>641</v>
+        <v>1122</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5302</v>
+        <v>3738</v>
       </c>
       <c r="C2" t="n">
-        <v>1823</v>
+        <v>4037</v>
       </c>
       <c r="D2" t="n">
-        <v>13784</v>
+        <v>14753</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6004</v>
+        <v>4164</v>
       </c>
       <c r="C3" t="n">
-        <v>5079</v>
+        <v>7410</v>
       </c>
       <c r="D3" t="n">
-        <v>16982</v>
+        <v>17006</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2908</v>
+        <v>2133</v>
       </c>
       <c r="C4" t="n">
-        <v>7339</v>
+        <v>7609</v>
       </c>
       <c r="D4" t="n">
-        <v>9415</v>
+        <v>10281</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1572</v>
+        <v>1245</v>
       </c>
       <c r="C5" t="n">
-        <v>4940</v>
+        <v>5656</v>
       </c>
       <c r="D5" t="n">
-        <v>3236</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>2615</v>
+        <v>4297</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>982</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>244</v>
       </c>
       <c r="C7" t="n">
-        <v>1542</v>
+        <v>2990</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>1472</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>495</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7050</v>
+        <v>4556</v>
       </c>
       <c r="C2" t="n">
-        <v>9033</v>
+        <v>6042</v>
       </c>
       <c r="D2" t="n">
-        <v>24709</v>
+        <v>18325</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4824</v>
+        <v>3354</v>
       </c>
       <c r="C3" t="n">
-        <v>3030</v>
+        <v>5171</v>
       </c>
       <c r="D3" t="n">
-        <v>15353</v>
+        <v>15556</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3661</v>
+        <v>2564</v>
       </c>
       <c r="C4" t="n">
-        <v>6085</v>
+        <v>7428</v>
       </c>
       <c r="D4" t="n">
-        <v>10436</v>
+        <v>11065</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1916</v>
+        <v>1420</v>
       </c>
       <c r="C5" t="n">
-        <v>6011</v>
+        <v>6419</v>
       </c>
       <c r="D5" t="n">
-        <v>4146</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1130</v>
+        <v>859</v>
       </c>
       <c r="C6" t="n">
-        <v>3707</v>
+        <v>4843</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>514</v>
+        <v>367</v>
       </c>
       <c r="C7" t="n">
-        <v>2040</v>
+        <v>3568</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>1142</v>
+        <v>2080</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>566</v>
+        <v>853</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>173</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4053</v>
+        <v>2694</v>
       </c>
       <c r="C2" t="n">
-        <v>4078</v>
+        <v>2898</v>
       </c>
       <c r="D2" t="n">
-        <v>17059</v>
+        <v>12789</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5200</v>
+        <v>3535</v>
       </c>
       <c r="C3" t="n">
-        <v>5012</v>
+        <v>5307</v>
       </c>
       <c r="D3" t="n">
-        <v>16032</v>
+        <v>15495</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4095</v>
+        <v>2802</v>
       </c>
       <c r="C4" t="n">
-        <v>5515</v>
+        <v>7342</v>
       </c>
       <c r="D4" t="n">
-        <v>11091</v>
+        <v>11690</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2015</v>
+        <v>1488</v>
       </c>
       <c r="C5" t="n">
-        <v>6819</v>
+        <v>7674</v>
       </c>
       <c r="D5" t="n">
-        <v>4506</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>955</v>
+        <v>680</v>
       </c>
       <c r="C6" t="n">
-        <v>4585</v>
+        <v>5849</v>
       </c>
       <c r="D6" t="n">
-        <v>1263</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>2149</v>
+        <v>3734</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>924</v>
+        <v>1447</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
+        <v>315</v>
+      </c>
+      <c r="D9" t="n">
         <v>282</v>
-      </c>
-      <c r="D9" t="n">
-        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4549</v>
+        <v>2754</v>
       </c>
       <c r="C2" t="n">
-        <v>3053</v>
+        <v>4115</v>
       </c>
       <c r="D2" t="n">
-        <v>19553</v>
+        <v>11924</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4008</v>
+        <v>2729</v>
       </c>
       <c r="C3" t="n">
-        <v>4054</v>
+        <v>3785</v>
       </c>
       <c r="D3" t="n">
-        <v>15230</v>
+        <v>14234</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4014</v>
+        <v>2696</v>
       </c>
       <c r="C4" t="n">
-        <v>5154</v>
+        <v>6251</v>
       </c>
       <c r="D4" t="n">
-        <v>11560</v>
+        <v>11919</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2538</v>
+        <v>1784</v>
       </c>
       <c r="C5" t="n">
-        <v>6129</v>
+        <v>7441</v>
       </c>
       <c r="D5" t="n">
-        <v>5380</v>
+        <v>5581</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1240</v>
+        <v>891</v>
       </c>
       <c r="C6" t="n">
-        <v>5617</v>
+        <v>6664</v>
       </c>
       <c r="D6" t="n">
-        <v>1725</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>3171</v>
+        <v>4577</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1409</v>
+        <v>2281</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>510</v>
+        <v>679</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3184</v>
+        <v>1865</v>
       </c>
       <c r="C2" t="n">
-        <v>1802</v>
+        <v>4081</v>
       </c>
       <c r="D2" t="n">
-        <v>13701</v>
+        <v>9926</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3668</v>
+        <v>2399</v>
       </c>
       <c r="C3" t="n">
-        <v>3327</v>
+        <v>3592</v>
       </c>
       <c r="D3" t="n">
-        <v>15076</v>
+        <v>13319</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3691</v>
+        <v>2465</v>
       </c>
       <c r="C4" t="n">
-        <v>4681</v>
+        <v>5270</v>
       </c>
       <c r="D4" t="n">
-        <v>11812</v>
+        <v>11959</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2837</v>
+        <v>1955</v>
       </c>
       <c r="C5" t="n">
-        <v>5862</v>
+        <v>7149</v>
       </c>
       <c r="D5" t="n">
-        <v>5980</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1471</v>
+        <v>1041</v>
       </c>
       <c r="C6" t="n">
-        <v>6018</v>
+        <v>7177</v>
       </c>
       <c r="D6" t="n">
-        <v>2105</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>220</v>
       </c>
       <c r="C7" t="n">
-        <v>4034</v>
+        <v>5380</v>
       </c>
       <c r="D7" t="n">
-        <v>745</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1872</v>
+        <v>2852</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>611</v>
+        <v>771</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4226</v>
+        <v>2596</v>
       </c>
       <c r="C2" t="n">
-        <v>8763</v>
+        <v>6787</v>
       </c>
       <c r="D2" t="n">
-        <v>12746</v>
+        <v>14607</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2930</v>
+        <v>1865</v>
       </c>
       <c r="C3" t="n">
-        <v>2402</v>
+        <v>3402</v>
       </c>
       <c r="D3" t="n">
-        <v>13911</v>
+        <v>12059</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3231</v>
+        <v>2122</v>
       </c>
       <c r="C4" t="n">
-        <v>3985</v>
+        <v>4467</v>
       </c>
       <c r="D4" t="n">
-        <v>11954</v>
+        <v>11791</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2856</v>
+        <v>1957</v>
       </c>
       <c r="C5" t="n">
-        <v>5241</v>
+        <v>6260</v>
       </c>
       <c r="D5" t="n">
-        <v>6638</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1816</v>
+        <v>1234</v>
       </c>
       <c r="C6" t="n">
-        <v>5902</v>
+        <v>7107</v>
       </c>
       <c r="D6" t="n">
-        <v>2598</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>653</v>
+        <v>423</v>
       </c>
       <c r="C7" t="n">
-        <v>4810</v>
+        <v>6029</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>880</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>2694</v>
+        <v>3745</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1049</v>
+        <v>1423</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="D10" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5194</v>
+        <v>4541</v>
       </c>
       <c r="C2" t="n">
-        <v>4281</v>
+        <v>12208</v>
       </c>
       <c r="D2" t="n">
-        <v>5679</v>
+        <v>11489</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2962</v>
+        <v>1877</v>
       </c>
       <c r="C2" t="n">
-        <v>4837</v>
+        <v>3909</v>
       </c>
       <c r="D2" t="n">
-        <v>9382</v>
+        <v>10867</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3926</v>
+        <v>2483</v>
       </c>
       <c r="C3" t="n">
-        <v>4179</v>
+        <v>4459</v>
       </c>
       <c r="D3" t="n">
-        <v>14858</v>
+        <v>13186</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4295</v>
+        <v>2893</v>
       </c>
       <c r="C4" t="n">
-        <v>5634</v>
+        <v>6598</v>
       </c>
       <c r="D4" t="n">
-        <v>12316</v>
+        <v>12142</v>
       </c>
     </row>
     <row r="5">
@@ -4243,10 +4243,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1783</v>
+        <v>1176</v>
       </c>
       <c r="C5" t="n">
-        <v>8033</v>
+        <v>9667</v>
       </c>
       <c r="D5" t="n">
         <v>6116</v>
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>603</v>
+        <v>390</v>
       </c>
       <c r="C6" t="n">
-        <v>5986</v>
+        <v>7231</v>
       </c>
       <c r="D6" t="n">
-        <v>2039</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2640</v>
+        <v>3670</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1028</v>
+        <v>1394</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6732</v>
+        <v>5396</v>
       </c>
       <c r="C2" t="n">
-        <v>5007</v>
+        <v>11477</v>
       </c>
       <c r="D2" t="n">
-        <v>15575</v>
+        <v>19051</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2207</v>
+        <v>1930</v>
       </c>
       <c r="C3" t="n">
-        <v>2191</v>
+        <v>6152</v>
       </c>
       <c r="D3" t="n">
-        <v>1638</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4931</v>
+        <v>4992</v>
       </c>
       <c r="C2" t="n">
-        <v>3228</v>
+        <v>7330</v>
       </c>
       <c r="D2" t="n">
-        <v>14227</v>
+        <v>32061</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3668</v>
+        <v>3007</v>
       </c>
       <c r="C3" t="n">
-        <v>3282</v>
+        <v>7904</v>
       </c>
       <c r="D3" t="n">
-        <v>3858</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>992</v>
+        <v>872</v>
       </c>
       <c r="C4" t="n">
-        <v>1347</v>
+        <v>3648</v>
       </c>
       <c r="D4" t="n">
-        <v>1511</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4864</v>
+        <v>5707</v>
       </c>
       <c r="C2" t="n">
-        <v>3692</v>
+        <v>12123</v>
       </c>
       <c r="D2" t="n">
-        <v>19714</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3534</v>
+        <v>3249</v>
       </c>
       <c r="C3" t="n">
-        <v>2841</v>
+        <v>6588</v>
       </c>
       <c r="D3" t="n">
-        <v>5239</v>
+        <v>9083</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2002</v>
+        <v>1623</v>
       </c>
       <c r="C4" t="n">
-        <v>2402</v>
+        <v>5941</v>
       </c>
       <c r="D4" t="n">
-        <v>1901</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>468</v>
+        <v>412</v>
       </c>
       <c r="C5" t="n">
-        <v>842</v>
+        <v>2060</v>
       </c>
       <c r="D5" t="n">
-        <v>1212</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5885</v>
+        <v>5741</v>
       </c>
       <c r="C2" t="n">
-        <v>7334</v>
+        <v>7858</v>
       </c>
       <c r="D2" t="n">
-        <v>22680</v>
+        <v>31103</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3463</v>
+        <v>3577</v>
       </c>
       <c r="C3" t="n">
-        <v>2856</v>
+        <v>8243</v>
       </c>
       <c r="D3" t="n">
-        <v>7070</v>
+        <v>11567</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2336</v>
+        <v>2020</v>
       </c>
       <c r="C4" t="n">
-        <v>2592</v>
+        <v>6095</v>
       </c>
       <c r="D4" t="n">
-        <v>2433</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1022</v>
+        <v>825</v>
       </c>
       <c r="C5" t="n">
-        <v>1640</v>
+        <v>3991</v>
       </c>
       <c r="D5" t="n">
-        <v>1300</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>579</v>
+        <v>1158</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
         <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>284</v>
@@ -5591,7 +5591,7 @@
         <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7569</v>
+        <v>5448</v>
       </c>
       <c r="C2" t="n">
-        <v>6998</v>
+        <v>5184</v>
       </c>
       <c r="D2" t="n">
-        <v>28191</v>
+        <v>26283</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>3321</v>
       </c>
       <c r="C3" t="n">
-        <v>4247</v>
+        <v>6608</v>
       </c>
       <c r="D3" t="n">
-        <v>8415</v>
+        <v>12766</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1799</v>
+        <v>1696</v>
       </c>
       <c r="C4" t="n">
-        <v>2227</v>
+        <v>5913</v>
       </c>
       <c r="D4" t="n">
-        <v>2776</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>887</v>
+        <v>724</v>
       </c>
       <c r="C5" t="n">
-        <v>1574</v>
+        <v>3644</v>
       </c>
       <c r="D5" t="n">
-        <v>1189</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="C6" t="n">
-        <v>757</v>
+        <v>1702</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>296</v>
+        <v>464</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5288</v>
+        <v>4342</v>
       </c>
       <c r="C2" t="n">
-        <v>6540</v>
+        <v>4049</v>
       </c>
       <c r="D2" t="n">
-        <v>26328</v>
+        <v>24460</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4598</v>
+        <v>3609</v>
       </c>
       <c r="C3" t="n">
-        <v>5065</v>
+        <v>5003</v>
       </c>
       <c r="D3" t="n">
-        <v>11262</v>
+        <v>14097</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2295</v>
+        <v>2179</v>
       </c>
       <c r="C4" t="n">
-        <v>3441</v>
+        <v>6197</v>
       </c>
       <c r="D4" t="n">
-        <v>3882</v>
+        <v>5696</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1198</v>
+        <v>1055</v>
       </c>
       <c r="C5" t="n">
-        <v>1936</v>
+        <v>4853</v>
       </c>
       <c r="D5" t="n">
-        <v>1461</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>562</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>1225</v>
+        <v>2727</v>
       </c>
       <c r="D6" t="n">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>562</v>
+        <v>1143</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>263</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>197</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4876</v>
+        <v>4589</v>
       </c>
       <c r="C2" t="n">
-        <v>7846</v>
+        <v>7701</v>
       </c>
       <c r="D2" t="n">
-        <v>28391</v>
+        <v>23285</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4077</v>
+        <v>3262</v>
       </c>
       <c r="C3" t="n">
-        <v>5087</v>
+        <v>3927</v>
       </c>
       <c r="D3" t="n">
-        <v>12964</v>
+        <v>14679</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2995</v>
+        <v>2466</v>
       </c>
       <c r="C4" t="n">
-        <v>4320</v>
+        <v>5366</v>
       </c>
       <c r="D4" t="n">
-        <v>5251</v>
+        <v>7055</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1533</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>2748</v>
+        <v>5461</v>
       </c>
       <c r="D5" t="n">
-        <v>1881</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>811</v>
+        <v>667</v>
       </c>
       <c r="C6" t="n">
-        <v>1587</v>
+        <v>3778</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>925</v>
+        <v>1923</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>421</v>
+        <v>738</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_20_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4292</v>
+        <v>671</v>
       </c>
       <c r="C2" t="n">
-        <v>7114</v>
+        <v>4011</v>
       </c>
       <c r="D2" t="n">
-        <v>26338</v>
+        <v>13710</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3162</v>
+        <v>1310</v>
       </c>
       <c r="C3" t="n">
-        <v>5013</v>
+        <v>9440</v>
       </c>
       <c r="D3" t="n">
-        <v>15049</v>
+        <v>14220</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2413</v>
+        <v>1046</v>
       </c>
       <c r="C4" t="n">
-        <v>4536</v>
+        <v>10462</v>
       </c>
       <c r="D4" t="n">
-        <v>8017</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1648</v>
+        <v>546</v>
       </c>
       <c r="C5" t="n">
-        <v>5301</v>
+        <v>6525</v>
       </c>
       <c r="D5" t="n">
-        <v>3118</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>4478</v>
+        <v>2733</v>
       </c>
       <c r="D6" t="n">
-        <v>1208</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>2776</v>
+        <v>899</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1253</v>
+        <v>360</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>473</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5227</v>
+        <v>772</v>
       </c>
       <c r="C2" t="n">
-        <v>6409</v>
+        <v>11954</v>
       </c>
       <c r="D2" t="n">
-        <v>29555</v>
+        <v>23233</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2982</v>
+        <v>871</v>
       </c>
       <c r="C3" t="n">
-        <v>5225</v>
+        <v>5842</v>
       </c>
       <c r="D3" t="n">
-        <v>15506</v>
+        <v>13277</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2325</v>
+        <v>1016</v>
       </c>
       <c r="C4" t="n">
-        <v>4613</v>
+        <v>9805</v>
       </c>
       <c r="D4" t="n">
-        <v>8776</v>
+        <v>7518</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1740</v>
+        <v>678</v>
       </c>
       <c r="C5" t="n">
-        <v>4852</v>
+        <v>8354</v>
       </c>
       <c r="D5" t="n">
-        <v>3775</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1087</v>
+        <v>326</v>
       </c>
       <c r="C6" t="n">
-        <v>4740</v>
+        <v>4551</v>
       </c>
       <c r="D6" t="n">
-        <v>1455</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>529</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>3492</v>
+        <v>1752</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>208</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1852</v>
+        <v>595</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>773</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7033</v>
+        <v>422</v>
       </c>
       <c r="C2" t="n">
-        <v>11770</v>
+        <v>5219</v>
       </c>
       <c r="D2" t="n">
-        <v>24182</v>
+        <v>15849</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3131</v>
+        <v>820</v>
       </c>
       <c r="C3" t="n">
-        <v>5063</v>
+        <v>7876</v>
       </c>
       <c r="D3" t="n">
-        <v>16199</v>
+        <v>14259</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2202</v>
+        <v>1097</v>
       </c>
       <c r="C4" t="n">
-        <v>4725</v>
+        <v>9190</v>
       </c>
       <c r="D4" t="n">
-        <v>9478</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1770</v>
+        <v>676</v>
       </c>
       <c r="C5" t="n">
-        <v>4654</v>
+        <v>9865</v>
       </c>
       <c r="D5" t="n">
-        <v>4296</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1213</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>4696</v>
+        <v>5482</v>
       </c>
       <c r="D6" t="n">
-        <v>1747</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>658</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>3933</v>
+        <v>1586</v>
       </c>
       <c r="D7" t="n">
-        <v>806</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>286</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2461</v>
+        <v>505</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1145</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>469</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6352</v>
+        <v>507</v>
       </c>
       <c r="C2" t="n">
-        <v>8191</v>
+        <v>4306</v>
       </c>
       <c r="D2" t="n">
-        <v>20123</v>
+        <v>21817</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3823</v>
+        <v>557</v>
       </c>
       <c r="C3" t="n">
-        <v>8125</v>
+        <v>5842</v>
       </c>
       <c r="D3" t="n">
-        <v>17685</v>
+        <v>13643</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1635</v>
+        <v>865</v>
       </c>
       <c r="C4" t="n">
-        <v>6962</v>
+        <v>8431</v>
       </c>
       <c r="D4" t="n">
-        <v>9156</v>
+        <v>8941</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1120</v>
+        <v>773</v>
       </c>
       <c r="C5" t="n">
-        <v>4602</v>
+        <v>9436</v>
       </c>
       <c r="D5" t="n">
-        <v>2866</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>607</v>
+        <v>379</v>
       </c>
       <c r="C6" t="n">
-        <v>3854</v>
+        <v>7472</v>
       </c>
       <c r="D6" t="n">
-        <v>789</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>2411</v>
+        <v>3220</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1122</v>
+        <v>917</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>459</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3738</v>
+        <v>324</v>
       </c>
       <c r="C2" t="n">
-        <v>4037</v>
+        <v>3289</v>
       </c>
       <c r="D2" t="n">
-        <v>14753</v>
+        <v>15347</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4164</v>
+        <v>472</v>
       </c>
       <c r="C3" t="n">
-        <v>7410</v>
+        <v>4759</v>
       </c>
       <c r="D3" t="n">
-        <v>17006</v>
+        <v>14056</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2133</v>
+        <v>711</v>
       </c>
       <c r="C4" t="n">
-        <v>7609</v>
+        <v>7323</v>
       </c>
       <c r="D4" t="n">
-        <v>10281</v>
+        <v>9386</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1245</v>
+        <v>791</v>
       </c>
       <c r="C5" t="n">
-        <v>5656</v>
+        <v>9216</v>
       </c>
       <c r="D5" t="n">
-        <v>3558</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>716</v>
+        <v>450</v>
       </c>
       <c r="C6" t="n">
-        <v>4297</v>
+        <v>8498</v>
       </c>
       <c r="D6" t="n">
-        <v>982</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>2990</v>
+        <v>4523</v>
       </c>
       <c r="D7" t="n">
-        <v>505</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1472</v>
+        <v>1394</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>495</v>
+        <v>404</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4556</v>
+        <v>714</v>
       </c>
       <c r="C2" t="n">
-        <v>6042</v>
+        <v>9307</v>
       </c>
       <c r="D2" t="n">
-        <v>18325</v>
+        <v>18582</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3354</v>
+        <v>351</v>
       </c>
       <c r="C3" t="n">
-        <v>5171</v>
+        <v>3703</v>
       </c>
       <c r="D3" t="n">
-        <v>15556</v>
+        <v>13299</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2564</v>
+        <v>542</v>
       </c>
       <c r="C4" t="n">
-        <v>7428</v>
+        <v>6038</v>
       </c>
       <c r="D4" t="n">
-        <v>11065</v>
+        <v>9817</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1420</v>
+        <v>709</v>
       </c>
       <c r="C5" t="n">
-        <v>6419</v>
+        <v>8224</v>
       </c>
       <c r="D5" t="n">
-        <v>4482</v>
+        <v>4796</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>859</v>
+        <v>529</v>
       </c>
       <c r="C6" t="n">
-        <v>4843</v>
+        <v>8795</v>
       </c>
       <c r="D6" t="n">
-        <v>1339</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>3568</v>
+        <v>6040</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>2080</v>
+        <v>2541</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>853</v>
+        <v>737</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2694</v>
+        <v>502</v>
       </c>
       <c r="C2" t="n">
-        <v>2898</v>
+        <v>5212</v>
       </c>
       <c r="D2" t="n">
-        <v>12789</v>
+        <v>13676</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3535</v>
+        <v>533</v>
       </c>
       <c r="C3" t="n">
-        <v>5307</v>
+        <v>5361</v>
       </c>
       <c r="D3" t="n">
-        <v>15495</v>
+        <v>14615</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2802</v>
+        <v>924</v>
       </c>
       <c r="C4" t="n">
-        <v>7342</v>
+        <v>8670</v>
       </c>
       <c r="D4" t="n">
-        <v>11690</v>
+        <v>9869</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1488</v>
+        <v>515</v>
       </c>
       <c r="C5" t="n">
-        <v>7674</v>
+        <v>12256</v>
       </c>
       <c r="D5" t="n">
-        <v>4722</v>
+        <v>4364</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>680</v>
+        <v>186</v>
       </c>
       <c r="C6" t="n">
-        <v>5849</v>
+        <v>7729</v>
       </c>
       <c r="D6" t="n">
-        <v>1306</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>3734</v>
+        <v>2490</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1447</v>
+        <v>722</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D10" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2754</v>
+        <v>258</v>
       </c>
       <c r="C2" t="n">
-        <v>4115</v>
+        <v>2716</v>
       </c>
       <c r="D2" t="n">
-        <v>11924</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2729</v>
+        <v>437</v>
       </c>
       <c r="C3" t="n">
-        <v>3785</v>
+        <v>4690</v>
       </c>
       <c r="D3" t="n">
-        <v>14234</v>
+        <v>13460</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2696</v>
+        <v>628</v>
       </c>
       <c r="C4" t="n">
-        <v>6251</v>
+        <v>6646</v>
       </c>
       <c r="D4" t="n">
-        <v>11919</v>
+        <v>9899</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1784</v>
+        <v>480</v>
       </c>
       <c r="C5" t="n">
-        <v>7441</v>
+        <v>9452</v>
       </c>
       <c r="D5" t="n">
-        <v>5581</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>891</v>
+        <v>177</v>
       </c>
       <c r="C6" t="n">
-        <v>6664</v>
+        <v>7787</v>
       </c>
       <c r="D6" t="n">
-        <v>1760</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>4577</v>
+        <v>3264</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2281</v>
+        <v>861</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>113</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1865</v>
+        <v>144</v>
       </c>
       <c r="C2" t="n">
-        <v>4081</v>
+        <v>10616</v>
       </c>
       <c r="D2" t="n">
-        <v>9926</v>
+        <v>9433</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2399</v>
+        <v>297</v>
       </c>
       <c r="C3" t="n">
-        <v>3592</v>
+        <v>3266</v>
       </c>
       <c r="D3" t="n">
-        <v>13319</v>
+        <v>12114</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2465</v>
+        <v>477</v>
       </c>
       <c r="C4" t="n">
-        <v>5270</v>
+        <v>5493</v>
       </c>
       <c r="D4" t="n">
-        <v>11959</v>
+        <v>10118</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1955</v>
+        <v>495</v>
       </c>
       <c r="C5" t="n">
-        <v>7149</v>
+        <v>7854</v>
       </c>
       <c r="D5" t="n">
-        <v>6134</v>
+        <v>5373</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1041</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>7177</v>
+        <v>8581</v>
       </c>
       <c r="D6" t="n">
-        <v>2120</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>5380</v>
+        <v>5345</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>2852</v>
+        <v>1928</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>771</v>
+        <v>505</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2596</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>6787</v>
+        <v>16779</v>
       </c>
       <c r="D2" t="n">
-        <v>14607</v>
+        <v>15150</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1865</v>
+        <v>196</v>
       </c>
       <c r="C3" t="n">
-        <v>3402</v>
+        <v>5760</v>
       </c>
       <c r="D3" t="n">
-        <v>12059</v>
+        <v>10935</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2122</v>
+        <v>351</v>
       </c>
       <c r="C4" t="n">
-        <v>4467</v>
+        <v>4278</v>
       </c>
       <c r="D4" t="n">
-        <v>11791</v>
+        <v>10136</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1957</v>
+        <v>442</v>
       </c>
       <c r="C5" t="n">
-        <v>6260</v>
+        <v>6602</v>
       </c>
       <c r="D5" t="n">
-        <v>6730</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1234</v>
+        <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>7107</v>
+        <v>8177</v>
       </c>
       <c r="D6" t="n">
-        <v>2593</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>423</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>6029</v>
+        <v>6738</v>
       </c>
       <c r="D7" t="n">
-        <v>880</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>3745</v>
+        <v>3314</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1423</v>
+        <v>1076</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>385</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4541</v>
+        <v>2819</v>
       </c>
       <c r="C2" t="n">
-        <v>12208</v>
+        <v>15803</v>
       </c>
       <c r="D2" t="n">
-        <v>11489</v>
+        <v>10620</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1877</v>
+        <v>225</v>
       </c>
       <c r="C2" t="n">
-        <v>3909</v>
+        <v>14736</v>
       </c>
       <c r="D2" t="n">
-        <v>10867</v>
+        <v>15937</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2483</v>
+        <v>118</v>
       </c>
       <c r="C3" t="n">
-        <v>4459</v>
+        <v>9002</v>
       </c>
       <c r="D3" t="n">
-        <v>13186</v>
+        <v>10740</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2893</v>
+        <v>256</v>
       </c>
       <c r="C4" t="n">
-        <v>6598</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="n">
-        <v>12142</v>
+        <v>9942</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1176</v>
+        <v>374</v>
       </c>
       <c r="C5" t="n">
-        <v>9667</v>
+        <v>5505</v>
       </c>
       <c r="D5" t="n">
-        <v>6116</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>390</v>
+        <v>347</v>
       </c>
       <c r="C6" t="n">
-        <v>7231</v>
+        <v>7406</v>
       </c>
       <c r="D6" t="n">
-        <v>2020</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>3670</v>
+        <v>7299</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1394</v>
+        <v>4555</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>377</v>
+        <v>1887</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>560</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5396</v>
+        <v>4454</v>
       </c>
       <c r="C2" t="n">
-        <v>11477</v>
+        <v>13299</v>
       </c>
       <c r="D2" t="n">
-        <v>19051</v>
+        <v>18271</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1930</v>
+        <v>912</v>
       </c>
       <c r="C3" t="n">
-        <v>6152</v>
+        <v>6240</v>
       </c>
       <c r="D3" t="n">
-        <v>2569</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4992</v>
+        <v>2996</v>
       </c>
       <c r="C2" t="n">
-        <v>7330</v>
+        <v>9706</v>
       </c>
       <c r="D2" t="n">
-        <v>32061</v>
+        <v>22375</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3007</v>
+        <v>2281</v>
       </c>
       <c r="C3" t="n">
-        <v>7904</v>
+        <v>9072</v>
       </c>
       <c r="D3" t="n">
-        <v>5148</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>872</v>
+        <v>449</v>
       </c>
       <c r="C4" t="n">
-        <v>3648</v>
+        <v>3882</v>
       </c>
       <c r="D4" t="n">
-        <v>1699</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5707</v>
+        <v>1653</v>
       </c>
       <c r="C2" t="n">
-        <v>12123</v>
+        <v>5036</v>
       </c>
       <c r="D2" t="n">
-        <v>30676</v>
+        <v>27870</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3249</v>
+        <v>2174</v>
       </c>
       <c r="C3" t="n">
-        <v>6588</v>
+        <v>8210</v>
       </c>
       <c r="D3" t="n">
-        <v>9083</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1623</v>
+        <v>1186</v>
       </c>
       <c r="C4" t="n">
-        <v>5941</v>
+        <v>6840</v>
       </c>
       <c r="D4" t="n">
-        <v>2309</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>412</v>
+        <v>235</v>
       </c>
       <c r="C5" t="n">
-        <v>2060</v>
+        <v>2283</v>
       </c>
       <c r="D5" t="n">
-        <v>1252</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5741</v>
+        <v>1221</v>
       </c>
       <c r="C2" t="n">
-        <v>7858</v>
+        <v>7633</v>
       </c>
       <c r="D2" t="n">
-        <v>31103</v>
+        <v>29636</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3577</v>
+        <v>1597</v>
       </c>
       <c r="C3" t="n">
-        <v>8243</v>
+        <v>5646</v>
       </c>
       <c r="D3" t="n">
-        <v>11567</v>
+        <v>10119</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2020</v>
+        <v>1424</v>
       </c>
       <c r="C4" t="n">
-        <v>6095</v>
+        <v>7460</v>
       </c>
       <c r="D4" t="n">
-        <v>3387</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>825</v>
+        <v>594</v>
       </c>
       <c r="C5" t="n">
-        <v>3991</v>
+        <v>4685</v>
       </c>
       <c r="D5" t="n">
-        <v>1396</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="C6" t="n">
-        <v>1158</v>
+        <v>1307</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5448</v>
+        <v>1395</v>
       </c>
       <c r="C2" t="n">
-        <v>5184</v>
+        <v>11364</v>
       </c>
       <c r="D2" t="n">
-        <v>26283</v>
+        <v>26257</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3321</v>
+        <v>1187</v>
       </c>
       <c r="C3" t="n">
-        <v>6608</v>
+        <v>5790</v>
       </c>
       <c r="D3" t="n">
-        <v>12766</v>
+        <v>12233</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1696</v>
+        <v>1291</v>
       </c>
       <c r="C4" t="n">
-        <v>5913</v>
+        <v>6364</v>
       </c>
       <c r="D4" t="n">
-        <v>4066</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>724</v>
+        <v>852</v>
       </c>
       <c r="C5" t="n">
-        <v>3644</v>
+        <v>5927</v>
       </c>
       <c r="D5" t="n">
-        <v>1374</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>1702</v>
+        <v>2947</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>464</v>
+        <v>781</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4342</v>
+        <v>1359</v>
       </c>
       <c r="C2" t="n">
-        <v>4049</v>
+        <v>14237</v>
       </c>
       <c r="D2" t="n">
-        <v>24460</v>
+        <v>24388</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3609</v>
+        <v>1055</v>
       </c>
       <c r="C3" t="n">
-        <v>5003</v>
+        <v>7415</v>
       </c>
       <c r="D3" t="n">
-        <v>14097</v>
+        <v>13318</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2179</v>
+        <v>1073</v>
       </c>
       <c r="C4" t="n">
-        <v>6197</v>
+        <v>5895</v>
       </c>
       <c r="D4" t="n">
-        <v>5696</v>
+        <v>5318</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1055</v>
+        <v>931</v>
       </c>
       <c r="C5" t="n">
-        <v>4853</v>
+        <v>6009</v>
       </c>
       <c r="D5" t="n">
-        <v>1849</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="C6" t="n">
-        <v>2727</v>
+        <v>4233</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>1143</v>
+        <v>1757</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>507</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4589</v>
+        <v>1275</v>
       </c>
       <c r="C2" t="n">
-        <v>7701</v>
+        <v>9111</v>
       </c>
       <c r="D2" t="n">
-        <v>23285</v>
+        <v>19503</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3262</v>
+        <v>1624</v>
       </c>
       <c r="C3" t="n">
-        <v>3927</v>
+        <v>11546</v>
       </c>
       <c r="D3" t="n">
-        <v>14679</v>
+        <v>14323</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2466</v>
+        <v>860</v>
       </c>
       <c r="C4" t="n">
-        <v>5366</v>
+        <v>9277</v>
       </c>
       <c r="D4" t="n">
-        <v>7055</v>
+        <v>4863</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>449</v>
       </c>
       <c r="C5" t="n">
-        <v>5461</v>
+        <v>4148</v>
       </c>
       <c r="D5" t="n">
-        <v>2439</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>667</v>
+        <v>166</v>
       </c>
       <c r="C6" t="n">
-        <v>3778</v>
+        <v>1721</v>
       </c>
       <c r="D6" t="n">
-        <v>1013</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>1923</v>
+        <v>496</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>738</v>
+        <v>273</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
